--- a/Result/checksun_type/塑膠材料.xlsx
+++ b/Result/checksun_type/塑膠材料.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>32.16</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>32.64</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>34.99</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>32.64</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>34.99</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>5050.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>4336.4</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>4336.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>5777.4</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>6847.0</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>6847</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-351.2719648777975</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>5050</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>5050.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>31.72</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>32.68</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>35.1</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>32.68</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>35.1</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>5616.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>4001.8</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>4001.8</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>5931.5</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>7423.62</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>7423.62</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-411.2842611585756</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>5616</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>5616.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>31.46</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>32.74</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>35.26</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>32.74</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>35.26</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>2561.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>3993.0</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>3993</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>5845.1</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>7707.14</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>7707.14</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>-542.9702465183082</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>2561</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>2561.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>31.64</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>32.9</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>35.47</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>32.9</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>35.47</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>4686.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>4282.2</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>4282.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>5931.0</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>7956.74</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>7956.74</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>-384.3798596565584</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>4686</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>4686.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>31.98</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>33.08</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>35.68</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>33.08</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>35.68</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>3769.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>4989.2</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>4989.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>5806.8</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>8223.9</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>8223.9</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-371.7728834377531</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>3769</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>3769.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>32.35</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>33.24</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>35.88</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>33.24</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>35.88</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>3377.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>7218.4</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>7218.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>6107.5</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>8475.5</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>8475.5</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-242.23531443097</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>3377</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>3377.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>32.85</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>33.42</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>36.09</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>33.42</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>36.09</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>5572.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>7861.2</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>7861.2</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>6235.6</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>9406.68</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>9406.68</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-6.530383191601686</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>5572</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>5572.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>33.15</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>33.56</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>36.32</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>33.56</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>36.32</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>4007.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>7697.2</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>7697.2</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>6678.3</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>11379.82</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>11379.82</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>95.24560369291066</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>4007</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>4007.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>33.18</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>33.67</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>36.47</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>33.67</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>36.47</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>8221.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>7579.8</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>7579.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>6844.8</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>11648.86</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>11648.86</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>404.9168133960384</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>8221</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>8221.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>33.13</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>33.78</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>36.62</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>33.78</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>36.62</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>14915.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>6624.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>6624.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>6226.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>12140.42</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>12140.42</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>381.3429410649342</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>14915</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>14915.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>32.96999999999999</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>33.82</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>36.81</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>33.82</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>36.81</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>6591.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>4996.6</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>4996.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>5294.2</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>15620.94</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>15620.94</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-383.1676958746775</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>6591</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>6591.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>27.52</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>27.81</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>28.56</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>27.81</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>28.56</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2990.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>2335.2</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>2335.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>4152.4</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>4273.74</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>4273.74</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-364.7263819266991</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2990</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2990.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>27.49</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>27.82</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>28.61</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>27.82</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>28.61</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>2015.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>2155.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>2155.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>4221.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>4426.5</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>4426.5</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>-400.3838891259043</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>2015</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>2015.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>27.47</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>27.84</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>28.68</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>27.84</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>28.68</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>1696.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>2964.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>2964.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>4414.8</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>4569.52</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>4569.52</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>-332.5594747988434</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>1696</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1696.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>27.67</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>27.87</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>28.76</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>27.87</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>28.76</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>2897.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3892.2</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3892.2</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>4421.9</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>4725.42</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>4725.42</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-189.6117588030834</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>2897</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>2897.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>28.01</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>27.9</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>28.85</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>27.9</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>28.85</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>2078.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>4374.8</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>4374.8</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>4283.4</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>4989.92</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>4989.92</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-107.3074588518875</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>2078</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2078.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>28.21</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>27.92</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>28.93</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>28.93</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2091.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>5969.6</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>5969.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>4293.1</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>5109.9</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>5109.9</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>101.8525217516744</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2091</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2091.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>28.37</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>27.96</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>29.02</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>27.96</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>29.02</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>6060.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>6287.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>6287.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>4687.3</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>5340.26</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>5340.26</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>395.6220468370602</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>6060</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>6060.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>28.43</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>27.98</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>29.09</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>27.98</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>29.09</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>6335.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>5865.2</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>5865.2</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>4545.2</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>5538.14</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>5538.14</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>375.9134381434305</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>6335</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>6335.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>28.26</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>27.97</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>29.16</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>27.97</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>29.16</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>5310.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>4951.6</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>4951.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>4094.7</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>5570.04</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>5570.04</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>304.868517218837</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>5310</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>5310.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>27.99</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>27.92</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>29.22</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>27.92</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>29.22</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>10052.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>4192.0</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>4192</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>4508.3</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>5774.94</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>5774.94</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>302.3090402830312</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>10052</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>10052.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>27.81</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>27.89</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>29.31</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>27.89</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>29.31</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>3680.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2616.6</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2616.6</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>3980.2</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>5865.78</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>5865.78</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-220.2155353496564</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>3680</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3680.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10465,7 +10333,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -10649,15 +10517,11 @@
           <t>99.67999999999999</t>
         </is>
       </c>
-      <c r="AM24" t="inlineStr">
-        <is>
-          <t>104.55</t>
-        </is>
-      </c>
-      <c r="AN24" t="inlineStr">
-        <is>
-          <t>114.62</t>
-        </is>
+      <c r="AM24" t="n">
+        <v>104.55</v>
+      </c>
+      <c r="AN24" t="n">
+        <v>114.62</v>
       </c>
       <c r="AO24" t="inlineStr">
         <is>
@@ -10704,20 +10568,16 @@
           <t>11298156.0</t>
         </is>
       </c>
-      <c r="AX24" t="inlineStr">
-        <is>
-          <t>9607693.8</t>
-        </is>
+      <c r="AX24" t="n">
+        <v>9607693.800000001</v>
       </c>
       <c r="AY24" t="inlineStr">
         <is>
           <t>11345070.4</t>
         </is>
       </c>
-      <c r="AZ24" t="inlineStr">
-        <is>
-          <t>19425437.44</t>
-        </is>
+      <c r="AZ24" t="n">
+        <v>19425437.44</v>
       </c>
       <c r="BA24" t="inlineStr">
         <is>
@@ -10734,8 +10594,10 @@
           <t>-1691198.742789451</t>
         </is>
       </c>
-      <c r="BD24" t="n">
-        <v>11298156</v>
+      <c r="BD24" t="inlineStr">
+        <is>
+          <t>11298156.0</t>
+        </is>
       </c>
       <c r="BE24" t="inlineStr">
         <is>
@@ -10901,7 +10763,7 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -11085,15 +10947,11 @@
           <t>99.1</t>
         </is>
       </c>
-      <c r="AM25" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="AN25" t="inlineStr">
-        <is>
-          <t>115.11</t>
-        </is>
+      <c r="AM25" t="n">
+        <v>105</v>
+      </c>
+      <c r="AN25" t="n">
+        <v>115.11</v>
       </c>
       <c r="AO25" t="inlineStr">
         <is>
@@ -11140,20 +10998,16 @@
           <t>8639149.0</t>
         </is>
       </c>
-      <c r="AX25" t="inlineStr">
-        <is>
-          <t>9476181.6</t>
-        </is>
+      <c r="AX25" t="n">
+        <v>9476181.6</v>
       </c>
       <c r="AY25" t="inlineStr">
         <is>
           <t>10578957.0</t>
         </is>
       </c>
-      <c r="AZ25" t="inlineStr">
-        <is>
-          <t>19597958.8</t>
-        </is>
+      <c r="AZ25" t="n">
+        <v>19597958.8</v>
       </c>
       <c r="BA25" t="inlineStr">
         <is>
@@ -11170,8 +11024,10 @@
           <t>-1980075.286180986</t>
         </is>
       </c>
-      <c r="BD25" t="n">
-        <v>8639149</v>
+      <c r="BD25" t="inlineStr">
+        <is>
+          <t>8639149.0</t>
+        </is>
       </c>
       <c r="BE25" t="inlineStr">
         <is>
@@ -11337,7 +11193,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -11521,15 +11377,11 @@
           <t>99.38</t>
         </is>
       </c>
-      <c r="AM26" t="inlineStr">
-        <is>
-          <t>105.44</t>
-        </is>
-      </c>
-      <c r="AN26" t="inlineStr">
-        <is>
-          <t>115.7</t>
-        </is>
+      <c r="AM26" t="n">
+        <v>105.44</v>
+      </c>
+      <c r="AN26" t="n">
+        <v>115.7</v>
       </c>
       <c r="AO26" t="inlineStr">
         <is>
@@ -11576,20 +11428,16 @@
           <t>4003587.0</t>
         </is>
       </c>
-      <c r="AX26" t="inlineStr">
-        <is>
-          <t>11584639.2</t>
-        </is>
+      <c r="AX26" t="n">
+        <v>11584639.2</v>
       </c>
       <c r="AY26" t="inlineStr">
         <is>
           <t>10218452.7</t>
         </is>
       </c>
-      <c r="AZ26" t="inlineStr">
-        <is>
-          <t>19921033.94</t>
-        </is>
+      <c r="AZ26" t="n">
+        <v>19921033.94</v>
       </c>
       <c r="BA26" t="inlineStr">
         <is>
@@ -11606,8 +11454,10 @@
           <t>-2037145.480805289</t>
         </is>
       </c>
-      <c r="BD26" t="n">
-        <v>4003587</v>
+      <c r="BD26" t="inlineStr">
+        <is>
+          <t>4003587.0</t>
+        </is>
       </c>
       <c r="BE26" t="inlineStr">
         <is>
@@ -11773,7 +11623,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -11957,15 +11807,11 @@
           <t>100.14</t>
         </is>
       </c>
-      <c r="AM27" t="inlineStr">
-        <is>
-          <t>105.94</t>
-        </is>
-      </c>
-      <c r="AN27" t="inlineStr">
-        <is>
-          <t>116.29</t>
-        </is>
+      <c r="AM27" t="n">
+        <v>105.94</v>
+      </c>
+      <c r="AN27" t="n">
+        <v>116.29</v>
       </c>
       <c r="AO27" t="inlineStr">
         <is>
@@ -12012,20 +11858,16 @@
           <t>13038996.0</t>
         </is>
       </c>
-      <c r="AX27" t="inlineStr">
-        <is>
-          <t>14979530.6</t>
-        </is>
+      <c r="AX27" t="n">
+        <v>14979530.6</v>
       </c>
       <c r="AY27" t="inlineStr">
         <is>
           <t>11649640.2</t>
         </is>
       </c>
-      <c r="AZ27" t="inlineStr">
-        <is>
-          <t>20326004.76</t>
-        </is>
+      <c r="AZ27" t="n">
+        <v>20326004.76</v>
       </c>
       <c r="BA27" t="inlineStr">
         <is>
@@ -12042,8 +11884,10 @@
           <t>-1549251.777382676</t>
         </is>
       </c>
-      <c r="BD27" t="n">
-        <v>13038996</v>
+      <c r="BD27" t="inlineStr">
+        <is>
+          <t>13038996.0</t>
+        </is>
       </c>
       <c r="BE27" t="inlineStr">
         <is>
@@ -12209,7 +12053,7 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -12393,15 +12237,11 @@
           <t>101.94</t>
         </is>
       </c>
-      <c r="AM28" t="inlineStr">
-        <is>
-          <t>106.48</t>
-        </is>
-      </c>
-      <c r="AN28" t="inlineStr">
-        <is>
-          <t>116.9</t>
-        </is>
+      <c r="AM28" t="n">
+        <v>106.48</v>
+      </c>
+      <c r="AN28" t="n">
+        <v>116.9</v>
       </c>
       <c r="AO28" t="inlineStr">
         <is>
@@ -12448,20 +12288,16 @@
           <t>11058581.0</t>
         </is>
       </c>
-      <c r="AX28" t="inlineStr">
-        <is>
-          <t>14273967.0</t>
-        </is>
+      <c r="AX28" t="n">
+        <v>14273967</v>
       </c>
       <c r="AY28" t="inlineStr">
         <is>
           <t>11459990.4</t>
         </is>
       </c>
-      <c r="AZ28" t="inlineStr">
-        <is>
-          <t>20451780.86</t>
-        </is>
+      <c r="AZ28" t="n">
+        <v>20451780.86</v>
       </c>
       <c r="BA28" t="inlineStr">
         <is>
@@ -12478,8 +12314,10 @@
           <t>-1765009.887586702</t>
         </is>
       </c>
-      <c r="BD28" t="n">
-        <v>11058581</v>
+      <c r="BD28" t="inlineStr">
+        <is>
+          <t>11058581.0</t>
+        </is>
       </c>
       <c r="BE28" t="inlineStr">
         <is>
@@ -12645,7 +12483,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -12829,15 +12667,11 @@
           <t>103.42</t>
         </is>
       </c>
-      <c r="AM29" t="inlineStr">
-        <is>
-          <t>107.06</t>
-        </is>
-      </c>
-      <c r="AN29" t="inlineStr">
-        <is>
-          <t>117.44</t>
-        </is>
+      <c r="AM29" t="n">
+        <v>107.06</v>
+      </c>
+      <c r="AN29" t="n">
+        <v>117.44</v>
       </c>
       <c r="AO29" t="inlineStr">
         <is>
@@ -12884,20 +12718,16 @@
           <t>10640595.0</t>
         </is>
       </c>
-      <c r="AX29" t="inlineStr">
-        <is>
-          <t>13082447.0</t>
-        </is>
+      <c r="AX29" t="n">
+        <v>13082447</v>
       </c>
       <c r="AY29" t="inlineStr">
         <is>
           <t>11572252.3</t>
         </is>
       </c>
-      <c r="AZ29" t="inlineStr">
-        <is>
-          <t>20461956.14</t>
-        </is>
+      <c r="AZ29" t="n">
+        <v>20461956.14</v>
       </c>
       <c r="BA29" t="inlineStr">
         <is>
@@ -12914,8 +12744,10 @@
           <t>-1798012.37046436</t>
         </is>
       </c>
-      <c r="BD29" t="n">
-        <v>10640595</v>
+      <c r="BD29" t="inlineStr">
+        <is>
+          <t>10640595.0</t>
+        </is>
       </c>
       <c r="BE29" t="inlineStr">
         <is>
@@ -13081,7 +12913,7 @@
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
@@ -13265,15 +13097,11 @@
           <t>105.0</t>
         </is>
       </c>
-      <c r="AM30" t="inlineStr">
-        <is>
-          <t>107.75</t>
-        </is>
-      </c>
-      <c r="AN30" t="inlineStr">
-        <is>
-          <t>117.98</t>
-        </is>
+      <c r="AM30" t="n">
+        <v>107.75</v>
+      </c>
+      <c r="AN30" t="n">
+        <v>117.98</v>
       </c>
       <c r="AO30" t="inlineStr">
         <is>
@@ -13320,20 +13148,16 @@
           <t>19181437.0</t>
         </is>
       </c>
-      <c r="AX30" t="inlineStr">
-        <is>
-          <t>11681732.4</t>
-        </is>
+      <c r="AX30" t="n">
+        <v>11681732.4</v>
       </c>
       <c r="AY30" t="inlineStr">
         <is>
           <t>11267888.0</t>
         </is>
       </c>
-      <c r="AZ30" t="inlineStr">
-        <is>
-          <t>20553347.06</t>
-        </is>
+      <c r="AZ30" t="n">
+        <v>20553347.06</v>
       </c>
       <c r="BA30" t="inlineStr">
         <is>
@@ -13350,8 +13174,10 @@
           <t>-1736159.832773</t>
         </is>
       </c>
-      <c r="BD30" t="n">
-        <v>19181437</v>
+      <c r="BD30" t="inlineStr">
+        <is>
+          <t>19181437.0</t>
+        </is>
       </c>
       <c r="BE30" t="inlineStr">
         <is>
@@ -13517,7 +13343,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -13701,15 +13527,11 @@
           <t>106.3</t>
         </is>
       </c>
-      <c r="AM31" t="inlineStr">
-        <is>
-          <t>108.55</t>
-        </is>
-      </c>
-      <c r="AN31" t="inlineStr">
-        <is>
-          <t>118.48</t>
-        </is>
+      <c r="AM31" t="n">
+        <v>108.55</v>
+      </c>
+      <c r="AN31" t="n">
+        <v>118.48</v>
       </c>
       <c r="AO31" t="inlineStr">
         <is>
@@ -13756,20 +13578,16 @@
           <t>20978044.0</t>
         </is>
       </c>
-      <c r="AX31" t="inlineStr">
-        <is>
-          <t>8852266.2</t>
-        </is>
+      <c r="AX31" t="n">
+        <v>8852266.199999999</v>
       </c>
       <c r="AY31" t="inlineStr">
         <is>
           <t>11199180.9</t>
         </is>
       </c>
-      <c r="AZ31" t="inlineStr">
-        <is>
-          <t>20515565.06</t>
-        </is>
+      <c r="AZ31" t="n">
+        <v>20515565.06</v>
       </c>
       <c r="BA31" t="inlineStr">
         <is>
@@ -13786,8 +13604,10 @@
           <t>-2500883.570614882</t>
         </is>
       </c>
-      <c r="BD31" t="n">
-        <v>20978044</v>
+      <c r="BD31" t="inlineStr">
+        <is>
+          <t>20978044.0</t>
+        </is>
       </c>
       <c r="BE31" t="inlineStr">
         <is>
@@ -13953,7 +13773,7 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -14137,15 +13957,11 @@
           <t>107.1</t>
         </is>
       </c>
-      <c r="AM32" t="inlineStr">
-        <is>
-          <t>109.35</t>
-        </is>
-      </c>
-      <c r="AN32" t="inlineStr">
-        <is>
-          <t>118.92</t>
-        </is>
+      <c r="AM32" t="n">
+        <v>109.35</v>
+      </c>
+      <c r="AN32" t="n">
+        <v>118.92</v>
       </c>
       <c r="AO32" t="inlineStr">
         <is>
@@ -14192,20 +14008,16 @@
           <t>9511178.0</t>
         </is>
       </c>
-      <c r="AX32" t="inlineStr">
-        <is>
-          <t>8319749.8</t>
-        </is>
+      <c r="AX32" t="n">
+        <v>8319749.8</v>
       </c>
       <c r="AY32" t="inlineStr">
         <is>
           <t>11464759.6</t>
         </is>
       </c>
-      <c r="AZ32" t="inlineStr">
-        <is>
-          <t>20864545.1</t>
-        </is>
+      <c r="AZ32" t="n">
+        <v>20864545.1</v>
       </c>
       <c r="BA32" t="inlineStr">
         <is>
@@ -14222,8 +14034,10 @@
           <t>-3696522.390009895</t>
         </is>
       </c>
-      <c r="BD32" t="n">
-        <v>9511178</v>
+      <c r="BD32" t="inlineStr">
+        <is>
+          <t>9511178.0</t>
+        </is>
       </c>
       <c r="BE32" t="inlineStr">
         <is>
@@ -14389,7 +14203,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
@@ -14573,15 +14387,11 @@
           <t>107.0</t>
         </is>
       </c>
-      <c r="AM33" t="inlineStr">
-        <is>
-          <t>110.02</t>
-        </is>
-      </c>
-      <c r="AN33" t="inlineStr">
-        <is>
-          <t>119.33</t>
-        </is>
+      <c r="AM33" t="n">
+        <v>110.02</v>
+      </c>
+      <c r="AN33" t="n">
+        <v>119.33</v>
       </c>
       <c r="AO33" t="inlineStr">
         <is>
@@ -14628,20 +14438,16 @@
           <t>5100981.0</t>
         </is>
       </c>
-      <c r="AX33" t="inlineStr">
-        <is>
-          <t>8646013.8</t>
-        </is>
+      <c r="AX33" t="n">
+        <v>8646013.800000001</v>
       </c>
       <c r="AY33" t="inlineStr">
         <is>
           <t>12611964.1</t>
         </is>
       </c>
-      <c r="AZ33" t="inlineStr">
-        <is>
-          <t>22452172.42</t>
-        </is>
+      <c r="AZ33" t="n">
+        <v>22452172.42</v>
       </c>
       <c r="BA33" t="inlineStr">
         <is>
@@ -14658,8 +14464,10 @@
           <t>-4043966.403788129</t>
         </is>
       </c>
-      <c r="BD33" t="n">
-        <v>5100981</v>
+      <c r="BD33" t="inlineStr">
+        <is>
+          <t>5100981.0</t>
+        </is>
       </c>
       <c r="BE33" t="inlineStr">
         <is>
@@ -14825,7 +14633,7 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -15009,15 +14817,11 @@
           <t>107.3</t>
         </is>
       </c>
-      <c r="AM34" t="inlineStr">
-        <is>
-          <t>110.55</t>
-        </is>
-      </c>
-      <c r="AN34" t="inlineStr">
-        <is>
-          <t>119.72</t>
-        </is>
+      <c r="AM34" t="n">
+        <v>110.55</v>
+      </c>
+      <c r="AN34" t="n">
+        <v>119.72</v>
       </c>
       <c r="AO34" t="inlineStr">
         <is>
@@ -15064,20 +14868,16 @@
           <t>3637022.0</t>
         </is>
       </c>
-      <c r="AX34" t="inlineStr">
-        <is>
-          <t>10062057.6</t>
-        </is>
+      <c r="AX34" t="n">
+        <v>10062057.6</v>
       </c>
       <c r="AY34" t="inlineStr">
         <is>
           <t>13855229.0</t>
         </is>
       </c>
-      <c r="AZ34" t="inlineStr">
-        <is>
-          <t>23007709.52</t>
-        </is>
+      <c r="AZ34" t="n">
+        <v>23007709.52</v>
       </c>
       <c r="BA34" t="inlineStr">
         <is>
@@ -15094,8 +14894,10 @@
           <t>-3923366.516193172</t>
         </is>
       </c>
-      <c r="BD34" t="n">
-        <v>3637022</v>
+      <c r="BD34" t="inlineStr">
+        <is>
+          <t>3637022.0</t>
+        </is>
       </c>
       <c r="BE34" t="inlineStr">
         <is>
@@ -15261,7 +15063,7 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【c】</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
@@ -15445,15 +15247,11 @@
           <t>1578.0</t>
         </is>
       </c>
-      <c r="AM35" t="inlineStr">
-        <is>
-          <t>1508.25</t>
-        </is>
-      </c>
-      <c r="AN35" t="inlineStr">
-        <is>
-          <t>1297.34</t>
-        </is>
+      <c r="AM35" t="n">
+        <v>1508.25</v>
+      </c>
+      <c r="AN35" t="n">
+        <v>1297.34</v>
       </c>
       <c r="AO35" t="inlineStr">
         <is>
@@ -15500,20 +15298,16 @@
           <t>8660559640.0</t>
         </is>
       </c>
-      <c r="AX35" t="inlineStr">
-        <is>
-          <t>12655765945.2</t>
-        </is>
+      <c r="AX35" t="n">
+        <v>12655765945.2</v>
       </c>
       <c r="AY35" t="inlineStr">
         <is>
           <t>9186859988.8</t>
         </is>
       </c>
-      <c r="AZ35" t="inlineStr">
-        <is>
-          <t>4926093528.12</t>
-        </is>
+      <c r="AZ35" t="n">
+        <v>4926093528.12</v>
       </c>
       <c r="BA35" t="inlineStr">
         <is>
@@ -15530,8 +15324,10 @@
           <t>1587065451.454584</t>
         </is>
       </c>
-      <c r="BD35" t="n">
-        <v>8660559640</v>
+      <c r="BD35" t="inlineStr">
+        <is>
+          <t>8660559640.0</t>
+        </is>
       </c>
       <c r="BE35" t="inlineStr">
         <is>
@@ -15697,7 +15493,7 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -15881,15 +15677,11 @@
           <t>1594.0</t>
         </is>
       </c>
-      <c r="AM36" t="inlineStr">
-        <is>
-          <t>1506.25</t>
-        </is>
-      </c>
-      <c r="AN36" t="inlineStr">
-        <is>
-          <t>1289.84</t>
-        </is>
+      <c r="AM36" t="n">
+        <v>1506.25</v>
+      </c>
+      <c r="AN36" t="n">
+        <v>1289.84</v>
       </c>
       <c r="AO36" t="inlineStr">
         <is>
@@ -15936,20 +15728,16 @@
           <t>14268998085.0</t>
         </is>
       </c>
-      <c r="AX36" t="inlineStr">
-        <is>
-          <t>11903064950.2</t>
-        </is>
+      <c r="AX36" t="n">
+        <v>11903064950.2</v>
       </c>
       <c r="AY36" t="inlineStr">
         <is>
           <t>8830581319.3</t>
         </is>
       </c>
-      <c r="AZ36" t="inlineStr">
-        <is>
-          <t>4817341249.12</t>
-        </is>
+      <c r="AZ36" t="n">
+        <v>4817341249.12</v>
       </c>
       <c r="BA36" t="inlineStr">
         <is>
@@ -15966,8 +15754,10 @@
           <t>2015843897.12149</t>
         </is>
       </c>
-      <c r="BD36" t="n">
-        <v>14268998085</v>
+      <c r="BD36" t="inlineStr">
+        <is>
+          <t>14268998085.0</t>
+        </is>
       </c>
       <c r="BE36" t="inlineStr">
         <is>
@@ -16133,7 +15923,7 @@
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
@@ -16317,15 +16107,11 @@
           <t>1599.0</t>
         </is>
       </c>
-      <c r="AM37" t="inlineStr">
-        <is>
-          <t>1501.25</t>
-        </is>
-      </c>
-      <c r="AN37" t="inlineStr">
-        <is>
-          <t>1281.64</t>
-        </is>
+      <c r="AM37" t="n">
+        <v>1501.25</v>
+      </c>
+      <c r="AN37" t="n">
+        <v>1281.64</v>
       </c>
       <c r="AO37" t="inlineStr">
         <is>
@@ -16372,20 +16158,16 @@
           <t>28742044615.0</t>
         </is>
       </c>
-      <c r="AX37" t="inlineStr">
-        <is>
-          <t>10298542898.2</t>
-        </is>
+      <c r="AX37" t="n">
+        <v>10298542898.2</v>
       </c>
       <c r="AY37" t="inlineStr">
         <is>
           <t>8042654289.3</t>
         </is>
       </c>
-      <c r="AZ37" t="inlineStr">
-        <is>
-          <t>4598697520.32</t>
-        </is>
+      <c r="AZ37" t="n">
+        <v>4598697520.32</v>
       </c>
       <c r="BA37" t="inlineStr">
         <is>
@@ -16402,8 +16184,10 @@
           <t>1955485989.784161</t>
         </is>
       </c>
-      <c r="BD37" t="n">
-        <v>28742044615</v>
+      <c r="BD37" t="inlineStr">
+        <is>
+          <t>28742044615.0</t>
+        </is>
       </c>
       <c r="BE37" t="inlineStr">
         <is>
@@ -16569,7 +16353,7 @@
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
@@ -16753,15 +16537,11 @@
           <t>1612.0</t>
         </is>
       </c>
-      <c r="AM38" t="inlineStr">
-        <is>
-          <t>1491.75</t>
-        </is>
-      </c>
-      <c r="AN38" t="inlineStr">
-        <is>
-          <t>1272.24</t>
-        </is>
+      <c r="AM38" t="n">
+        <v>1491.75</v>
+      </c>
+      <c r="AN38" t="n">
+        <v>1272.24</v>
       </c>
       <c r="AO38" t="inlineStr">
         <is>
@@ -16808,20 +16588,16 @@
           <t>6169714440.0</t>
         </is>
       </c>
-      <c r="AX38" t="inlineStr">
-        <is>
-          <t>5728226103.0</t>
-        </is>
+      <c r="AX38" t="n">
+        <v>5728226103</v>
       </c>
       <c r="AY38" t="inlineStr">
         <is>
           <t>5811772650.8</t>
         </is>
       </c>
-      <c r="AZ38" t="inlineStr">
-        <is>
-          <t>4091228347.42</t>
-        </is>
+      <c r="AZ38" t="n">
+        <v>4091228347.42</v>
       </c>
       <c r="BA38" t="inlineStr">
         <is>
@@ -16838,8 +16614,10 @@
           <t>248738065.7385426</t>
         </is>
       </c>
-      <c r="BD38" t="n">
-        <v>6169714440</v>
+      <c r="BD38" t="inlineStr">
+        <is>
+          <t>6169714440.0</t>
+        </is>
       </c>
       <c r="BE38" t="inlineStr">
         <is>
@@ -17005,7 +16783,7 @@
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
@@ -17189,15 +16967,11 @@
           <t>1595.0</t>
         </is>
       </c>
-      <c r="AM39" t="inlineStr">
-        <is>
-          <t>1478.0</t>
-        </is>
-      </c>
-      <c r="AN39" t="inlineStr">
-        <is>
-          <t>1261.84</t>
-        </is>
+      <c r="AM39" t="n">
+        <v>1478</v>
+      </c>
+      <c r="AN39" t="n">
+        <v>1261.84</v>
       </c>
       <c r="AO39" t="inlineStr">
         <is>
@@ -17244,20 +17018,16 @@
           <t>5437512946.0</t>
         </is>
       </c>
-      <c r="AX39" t="inlineStr">
-        <is>
-          <t>5661854900.6</t>
-        </is>
+      <c r="AX39" t="n">
+        <v>5661854900.6</v>
       </c>
       <c r="AY39" t="inlineStr">
         <is>
           <t>5608775910.3</t>
         </is>
       </c>
-      <c r="AZ39" t="inlineStr">
-        <is>
-          <t>4014085333.32</t>
-        </is>
+      <c r="AZ39" t="n">
+        <v>4014085333.32</v>
       </c>
       <c r="BA39" t="inlineStr">
         <is>
@@ -17274,8 +17044,10 @@
           <t>220107190.6469994</t>
         </is>
       </c>
-      <c r="BD39" t="n">
-        <v>5437512946</v>
+      <c r="BD39" t="inlineStr">
+        <is>
+          <t>5437512946.0</t>
+        </is>
       </c>
       <c r="BE39" t="inlineStr">
         <is>
@@ -17441,7 +17213,7 @@
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
@@ -17625,15 +17397,11 @@
           <t>1580.0</t>
         </is>
       </c>
-      <c r="AM40" t="inlineStr">
-        <is>
-          <t>1460.0</t>
-        </is>
-      </c>
-      <c r="AN40" t="inlineStr">
-        <is>
-          <t>1249.74</t>
-        </is>
+      <c r="AM40" t="n">
+        <v>1460</v>
+      </c>
+      <c r="AN40" t="n">
+        <v>1249.74</v>
       </c>
       <c r="AO40" t="inlineStr">
         <is>
@@ -17680,20 +17448,16 @@
           <t>4897054665.0</t>
         </is>
       </c>
-      <c r="AX40" t="inlineStr">
-        <is>
-          <t>5717954032.4</t>
-        </is>
+      <c r="AX40" t="n">
+        <v>5717954032.4</v>
       </c>
       <c r="AY40" t="inlineStr">
         <is>
           <t>5414291186.7</t>
         </is>
       </c>
-      <c r="AZ40" t="inlineStr">
-        <is>
-          <t>4036813613.2</t>
-        </is>
+      <c r="AZ40" t="n">
+        <v>4036813613.2</v>
       </c>
       <c r="BA40" t="inlineStr">
         <is>
@@ -17710,8 +17474,10 @@
           <t>249795129.4931173</t>
         </is>
       </c>
-      <c r="BD40" t="n">
-        <v>4897054665</v>
+      <c r="BD40" t="inlineStr">
+        <is>
+          <t>4897054665.0</t>
+        </is>
       </c>
       <c r="BE40" t="inlineStr">
         <is>
@@ -17877,7 +17643,7 @@
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
@@ -18061,15 +17827,11 @@
           <t>1564.0</t>
         </is>
       </c>
-      <c r="AM41" t="inlineStr">
-        <is>
-          <t>1445.5</t>
-        </is>
-      </c>
-      <c r="AN41" t="inlineStr">
-        <is>
-          <t>1239.34</t>
-        </is>
+      <c r="AM41" t="n">
+        <v>1445.5</v>
+      </c>
+      <c r="AN41" t="n">
+        <v>1239.34</v>
       </c>
       <c r="AO41" t="inlineStr">
         <is>
@@ -18116,20 +17878,16 @@
           <t>6246387825.0</t>
         </is>
       </c>
-      <c r="AX41" t="inlineStr">
-        <is>
-          <t>5758097688.4</t>
-        </is>
+      <c r="AX41" t="n">
+        <v>5758097688.4</v>
       </c>
       <c r="AY41" t="inlineStr">
         <is>
           <t>5400232874.2</t>
         </is>
       </c>
-      <c r="AZ41" t="inlineStr">
-        <is>
-          <t>4111558830.4</t>
-        </is>
+      <c r="AZ41" t="n">
+        <v>4111558830.4</v>
       </c>
       <c r="BA41" t="inlineStr">
         <is>
@@ -18146,8 +17904,10 @@
           <t>341191460.4699583</t>
         </is>
       </c>
-      <c r="BD41" t="n">
-        <v>6246387825</v>
+      <c r="BD41" t="inlineStr">
+        <is>
+          <t>6246387825.0</t>
+        </is>
       </c>
       <c r="BE41" t="inlineStr">
         <is>
@@ -18313,7 +18073,7 @@
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
@@ -18497,15 +18257,11 @@
           <t>1560.0</t>
         </is>
       </c>
-      <c r="AM42" t="inlineStr">
-        <is>
-          <t>1431.5</t>
-        </is>
-      </c>
-      <c r="AN42" t="inlineStr">
-        <is>
-          <t>1227.28</t>
-        </is>
+      <c r="AM42" t="n">
+        <v>1431.5</v>
+      </c>
+      <c r="AN42" t="n">
+        <v>1227.28</v>
       </c>
       <c r="AO42" t="inlineStr">
         <is>
@@ -18552,20 +18308,16 @@
           <t>5890460639.0</t>
         </is>
       </c>
-      <c r="AX42" t="inlineStr">
-        <is>
-          <t>5786765680.4</t>
-        </is>
+      <c r="AX42" t="n">
+        <v>5786765680.4</v>
       </c>
       <c r="AY42" t="inlineStr">
         <is>
           <t>5177128699.2</t>
         </is>
       </c>
-      <c r="AZ42" t="inlineStr">
-        <is>
-          <t>4046244405.4</t>
-        </is>
+      <c r="AZ42" t="n">
+        <v>4046244405.4</v>
       </c>
       <c r="BA42" t="inlineStr">
         <is>
@@ -18582,8 +18334,10 @@
           <t>315000828.2772322</t>
         </is>
       </c>
-      <c r="BD42" t="n">
-        <v>5890460639</v>
+      <c r="BD42" t="inlineStr">
+        <is>
+          <t>5890460639.0</t>
+        </is>
       </c>
       <c r="BE42" t="inlineStr">
         <is>
@@ -18749,7 +18503,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
@@ -18933,15 +18687,11 @@
           <t>1542.0</t>
         </is>
       </c>
-      <c r="AM43" t="inlineStr">
-        <is>
-          <t>1415.0</t>
-        </is>
-      </c>
-      <c r="AN43" t="inlineStr">
-        <is>
-          <t>1213.96</t>
-        </is>
+      <c r="AM43" t="n">
+        <v>1415</v>
+      </c>
+      <c r="AN43" t="n">
+        <v>1213.96</v>
       </c>
       <c r="AO43" t="inlineStr">
         <is>
@@ -18988,20 +18738,16 @@
           <t>5837858428.0</t>
         </is>
       </c>
-      <c r="AX43" t="inlineStr">
-        <is>
-          <t>5895319198.6</t>
-        </is>
+      <c r="AX43" t="n">
+        <v>5895319198.6</v>
       </c>
       <c r="AY43" t="inlineStr">
         <is>
           <t>5008164336.8</t>
         </is>
       </c>
-      <c r="AZ43" t="inlineStr">
-        <is>
-          <t>4019510992.36</t>
-        </is>
+      <c r="AZ43" t="n">
+        <v>4019510992.36</v>
       </c>
       <c r="BA43" t="inlineStr">
         <is>
@@ -19018,8 +18764,10 @@
           <t>304470665.4920092</t>
         </is>
       </c>
-      <c r="BD43" t="n">
-        <v>5837858428</v>
+      <c r="BD43" t="inlineStr">
+        <is>
+          <t>5837858428.0</t>
+        </is>
       </c>
       <c r="BE43" t="inlineStr">
         <is>
@@ -19185,7 +18933,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -19369,15 +19117,11 @@
           <t>1521.0</t>
         </is>
       </c>
-      <c r="AM44" t="inlineStr">
-        <is>
-          <t>1400.0</t>
-        </is>
-      </c>
-      <c r="AN44" t="inlineStr">
-        <is>
-          <t>1203.08</t>
-        </is>
+      <c r="AM44" t="n">
+        <v>1400</v>
+      </c>
+      <c r="AN44" t="n">
+        <v>1203.08</v>
       </c>
       <c r="AO44" t="inlineStr">
         <is>
@@ -19424,20 +19168,16 @@
           <t>5718008605.0</t>
         </is>
       </c>
-      <c r="AX44" t="inlineStr">
-        <is>
-          <t>5555696920.0</t>
-        </is>
+      <c r="AX44" t="n">
+        <v>5555696920</v>
       </c>
       <c r="AY44" t="inlineStr">
         <is>
           <t>4684194498.0</t>
         </is>
       </c>
-      <c r="AZ44" t="inlineStr">
-        <is>
-          <t>4026606885.46</t>
-        </is>
+      <c r="AZ44" t="n">
+        <v>4026606885.46</v>
       </c>
       <c r="BA44" t="inlineStr">
         <is>
@@ -19454,8 +19194,10 @@
           <t>284189574.6384048</t>
         </is>
       </c>
-      <c r="BD44" t="n">
-        <v>5718008605</v>
+      <c r="BD44" t="inlineStr">
+        <is>
+          <t>5718008605.0</t>
+        </is>
       </c>
       <c r="BE44" t="inlineStr">
         <is>
@@ -19621,7 +19363,7 @@
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
@@ -19805,15 +19547,11 @@
           <t>1474.0</t>
         </is>
       </c>
-      <c r="AM45" t="inlineStr">
-        <is>
-          <t>1379.0</t>
-        </is>
-      </c>
-      <c r="AN45" t="inlineStr">
-        <is>
-          <t>1192.48</t>
-        </is>
+      <c r="AM45" t="n">
+        <v>1379</v>
+      </c>
+      <c r="AN45" t="n">
+        <v>1192.48</v>
       </c>
       <c r="AO45" t="inlineStr">
         <is>
@@ -19860,20 +19598,16 @@
           <t>5097772945.0</t>
         </is>
       </c>
-      <c r="AX45" t="inlineStr">
-        <is>
-          <t>5110628341.0</t>
-        </is>
+      <c r="AX45" t="n">
+        <v>5110628341</v>
       </c>
       <c r="AY45" t="inlineStr">
         <is>
           <t>4542311051.0</t>
         </is>
       </c>
-      <c r="AZ45" t="inlineStr">
-        <is>
-          <t>4058950208.26</t>
-        </is>
+      <c r="AZ45" t="n">
+        <v>4058950208.26</v>
       </c>
       <c r="BA45" t="inlineStr">
         <is>
@@ -19890,8 +19624,10 @@
           <t>257908012.5033131</t>
         </is>
       </c>
-      <c r="BD45" t="n">
-        <v>5097772945</v>
+      <c r="BD45" t="inlineStr">
+        <is>
+          <t>5097772945.0</t>
+        </is>
       </c>
       <c r="BE45" t="inlineStr">
         <is>
@@ -20057,7 +19793,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>價_量;【b】</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
@@ -20241,15 +19977,11 @@
           <t>105.3</t>
         </is>
       </c>
-      <c r="AM46" t="inlineStr">
-        <is>
-          <t>99.52</t>
-        </is>
-      </c>
-      <c r="AN46" t="inlineStr">
-        <is>
-          <t>96.51</t>
-        </is>
+      <c r="AM46" t="n">
+        <v>99.52</v>
+      </c>
+      <c r="AN46" t="n">
+        <v>96.51000000000001</v>
       </c>
       <c r="AO46" t="inlineStr">
         <is>
@@ -20296,20 +20028,16 @@
           <t>85287514.0</t>
         </is>
       </c>
-      <c r="AX46" t="inlineStr">
-        <is>
-          <t>151213318.8</t>
-        </is>
+      <c r="AX46" t="n">
+        <v>151213318.8</v>
       </c>
       <c r="AY46" t="inlineStr">
         <is>
           <t>151318475.9</t>
         </is>
       </c>
-      <c r="AZ46" t="inlineStr">
-        <is>
-          <t>91042396.88</t>
-        </is>
+      <c r="AZ46" t="n">
+        <v>91042396.88</v>
       </c>
       <c r="BA46" t="inlineStr">
         <is>
@@ -20326,8 +20054,10 @@
           <t>2711461.138127059</t>
         </is>
       </c>
-      <c r="BD46" t="n">
-        <v>85287514</v>
+      <c r="BD46" t="inlineStr">
+        <is>
+          <t>85287514.0</t>
+        </is>
       </c>
       <c r="BE46" t="inlineStr">
         <is>
@@ -20493,7 +20223,7 @@
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -20677,15 +20407,11 @@
           <t>104.3</t>
         </is>
       </c>
-      <c r="AM47" t="inlineStr">
-        <is>
-          <t>98.73</t>
-        </is>
-      </c>
-      <c r="AN47" t="inlineStr">
-        <is>
-          <t>96.33</t>
-        </is>
+      <c r="AM47" t="n">
+        <v>98.73</v>
+      </c>
+      <c r="AN47" t="n">
+        <v>96.33</v>
       </c>
       <c r="AO47" t="inlineStr">
         <is>
@@ -20732,20 +20458,16 @@
           <t>217044233.0</t>
         </is>
       </c>
-      <c r="AX47" t="inlineStr">
-        <is>
-          <t>151864079.6</t>
-        </is>
+      <c r="AX47" t="n">
+        <v>151864079.6</v>
       </c>
       <c r="AY47" t="inlineStr">
         <is>
           <t>171702620.0</t>
         </is>
       </c>
-      <c r="AZ47" t="inlineStr">
-        <is>
-          <t>90320956.04</t>
-        </is>
+      <c r="AZ47" t="n">
+        <v>90320956.04000001</v>
       </c>
       <c r="BA47" t="inlineStr">
         <is>
@@ -20762,8 +20484,10 @@
           <t>9994869.517893165</t>
         </is>
       </c>
-      <c r="BD47" t="n">
-        <v>217044233</v>
+      <c r="BD47" t="inlineStr">
+        <is>
+          <t>217044233.0</t>
+        </is>
       </c>
       <c r="BE47" t="inlineStr">
         <is>
@@ -20929,7 +20653,7 @@
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -21113,15 +20837,11 @@
           <t>102.9</t>
         </is>
       </c>
-      <c r="AM48" t="inlineStr">
-        <is>
-          <t>97.92</t>
-        </is>
-      </c>
-      <c r="AN48" t="inlineStr">
-        <is>
-          <t>96.16</t>
-        </is>
+      <c r="AM48" t="n">
+        <v>97.92</v>
+      </c>
+      <c r="AN48" t="n">
+        <v>96.16</v>
       </c>
       <c r="AO48" t="inlineStr">
         <is>
@@ -21168,20 +20888,16 @@
           <t>159600272.0</t>
         </is>
       </c>
-      <c r="AX48" t="inlineStr">
-        <is>
-          <t>134412279.8</t>
-        </is>
+      <c r="AX48" t="n">
+        <v>134412279.8</v>
       </c>
       <c r="AY48" t="inlineStr">
         <is>
           <t>168766249.4</t>
         </is>
       </c>
-      <c r="AZ48" t="inlineStr">
-        <is>
-          <t>87040848.98</t>
-        </is>
+      <c r="AZ48" t="n">
+        <v>87040848.98</v>
       </c>
       <c r="BA48" t="inlineStr">
         <is>
@@ -21198,8 +20914,10 @@
           <t>5925987.684777111</t>
         </is>
       </c>
-      <c r="BD48" t="n">
-        <v>159600272</v>
+      <c r="BD48" t="inlineStr">
+        <is>
+          <t>159600272.0</t>
+        </is>
       </c>
       <c r="BE48" t="inlineStr">
         <is>
@@ -21365,7 +21083,7 @@
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
@@ -21549,15 +21267,11 @@
           <t>102.7</t>
         </is>
       </c>
-      <c r="AM49" t="inlineStr">
-        <is>
-          <t>97.32</t>
-        </is>
-      </c>
-      <c r="AN49" t="inlineStr">
-        <is>
-          <t>96.05</t>
-        </is>
+      <c r="AM49" t="n">
+        <v>97.31999999999999</v>
+      </c>
+      <c r="AN49" t="n">
+        <v>96.05</v>
       </c>
       <c r="AO49" t="inlineStr">
         <is>
@@ -21604,20 +21318,16 @@
           <t>152247091.0</t>
         </is>
       </c>
-      <c r="AX49" t="inlineStr">
-        <is>
-          <t>131651785.8</t>
-        </is>
+      <c r="AX49" t="n">
+        <v>131651785.8</v>
       </c>
       <c r="AY49" t="inlineStr">
         <is>
           <t>188252615.4</t>
         </is>
       </c>
-      <c r="AZ49" t="inlineStr">
-        <is>
-          <t>84978583.08</t>
-        </is>
+      <c r="AZ49" t="n">
+        <v>84978583.08</v>
       </c>
       <c r="BA49" t="inlineStr">
         <is>
@@ -21634,8 +21344,10 @@
           <t>6056367.041583598</t>
         </is>
       </c>
-      <c r="BD49" t="n">
-        <v>152247091</v>
+      <c r="BD49" t="inlineStr">
+        <is>
+          <t>152247091.0</t>
+        </is>
       </c>
       <c r="BE49" t="inlineStr">
         <is>
@@ -21801,7 +21513,7 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
@@ -21985,15 +21697,11 @@
           <t>102.9</t>
         </is>
       </c>
-      <c r="AM50" t="inlineStr">
-        <is>
-          <t>96.76</t>
-        </is>
-      </c>
-      <c r="AN50" t="inlineStr">
-        <is>
-          <t>95.96</t>
-        </is>
+      <c r="AM50" t="n">
+        <v>96.76000000000001</v>
+      </c>
+      <c r="AN50" t="n">
+        <v>95.95999999999999</v>
       </c>
       <c r="AO50" t="inlineStr">
         <is>
@@ -22040,20 +21748,16 @@
           <t>141887484.0</t>
         </is>
       </c>
-      <c r="AX50" t="inlineStr">
-        <is>
-          <t>132448333.4</t>
-        </is>
+      <c r="AX50" t="n">
+        <v>132448333.4</v>
       </c>
       <c r="AY50" t="inlineStr">
         <is>
           <t>196531473.3</t>
         </is>
       </c>
-      <c r="AZ50" t="inlineStr">
-        <is>
-          <t>82918302.5</t>
-        </is>
+      <c r="AZ50" t="n">
+        <v>82918302.5</v>
       </c>
       <c r="BA50" t="inlineStr">
         <is>
@@ -22070,8 +21774,10 @@
           <t>6814165.264107674</t>
         </is>
       </c>
-      <c r="BD50" t="n">
-        <v>141887484</v>
+      <c r="BD50" t="inlineStr">
+        <is>
+          <t>141887484.0</t>
+        </is>
       </c>
       <c r="BE50" t="inlineStr">
         <is>
@@ -22237,7 +21943,7 @@
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
@@ -22421,15 +22127,11 @@
           <t>102.9</t>
         </is>
       </c>
-      <c r="AM51" t="inlineStr">
-        <is>
-          <t>96.18</t>
-        </is>
-      </c>
-      <c r="AN51" t="inlineStr">
-        <is>
-          <t>95.82</t>
-        </is>
+      <c r="AM51" t="n">
+        <v>96.18000000000001</v>
+      </c>
+      <c r="AN51" t="n">
+        <v>95.81999999999999</v>
       </c>
       <c r="AO51" t="inlineStr">
         <is>
@@ -22476,20 +22178,16 @@
           <t>88541318.0</t>
         </is>
       </c>
-      <c r="AX51" t="inlineStr">
-        <is>
-          <t>151423633.0</t>
-        </is>
+      <c r="AX51" t="n">
+        <v>151423633</v>
       </c>
       <c r="AY51" t="inlineStr">
         <is>
           <t>196000867.3</t>
         </is>
       </c>
-      <c r="AZ51" t="inlineStr">
-        <is>
-          <t>80594523.88</t>
-        </is>
+      <c r="AZ51" t="n">
+        <v>80594523.88</v>
       </c>
       <c r="BA51" t="inlineStr">
         <is>
@@ -22506,8 +22204,10 @@
           <t>8763329.00113827</t>
         </is>
       </c>
-      <c r="BD51" t="n">
-        <v>88541318</v>
+      <c r="BD51" t="inlineStr">
+        <is>
+          <t>88541318.0</t>
+        </is>
       </c>
       <c r="BE51" t="inlineStr">
         <is>
@@ -22673,7 +22373,7 @@
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【b】</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
@@ -22857,15 +22557,11 @@
           <t>103.3</t>
         </is>
       </c>
-      <c r="AM52" t="inlineStr">
-        <is>
-          <t>95.75</t>
-        </is>
-      </c>
-      <c r="AN52" t="inlineStr">
-        <is>
-          <t>95.74</t>
-        </is>
+      <c r="AM52" t="n">
+        <v>95.75</v>
+      </c>
+      <c r="AN52" t="n">
+        <v>95.73999999999999</v>
       </c>
       <c r="AO52" t="inlineStr">
         <is>
@@ -22912,20 +22608,16 @@
           <t>129785234.0</t>
         </is>
       </c>
-      <c r="AX52" t="inlineStr">
-        <is>
-          <t>191541160.4</t>
-        </is>
+      <c r="AX52" t="n">
+        <v>191541160.4</v>
       </c>
       <c r="AY52" t="inlineStr">
         <is>
           <t>194097538.2</t>
         </is>
       </c>
-      <c r="AZ52" t="inlineStr">
-        <is>
-          <t>79445022.76</t>
-        </is>
+      <c r="AZ52" t="n">
+        <v>79445022.76000001</v>
       </c>
       <c r="BA52" t="inlineStr">
         <is>
@@ -22942,8 +22634,10 @@
           <t>16950533.2325699</t>
         </is>
       </c>
-      <c r="BD52" t="n">
-        <v>129785234</v>
+      <c r="BD52" t="inlineStr">
+        <is>
+          <t>129785234.0</t>
+        </is>
       </c>
       <c r="BE52" t="inlineStr">
         <is>
@@ -23109,7 +22803,7 @@
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
@@ -23293,15 +22987,11 @@
           <t>103.4</t>
         </is>
       </c>
-      <c r="AM53" t="inlineStr">
-        <is>
-          <t>95.38</t>
-        </is>
-      </c>
-      <c r="AN53" t="inlineStr">
-        <is>
-          <t>95.67</t>
-        </is>
+      <c r="AM53" t="n">
+        <v>95.38</v>
+      </c>
+      <c r="AN53" t="n">
+        <v>95.67</v>
       </c>
       <c r="AO53" t="inlineStr">
         <is>
@@ -23348,20 +23038,16 @@
           <t>145797802.0</t>
         </is>
       </c>
-      <c r="AX53" t="inlineStr">
-        <is>
-          <t>203120219.0</t>
-        </is>
+      <c r="AX53" t="n">
+        <v>203120219</v>
       </c>
       <c r="AY53" t="inlineStr">
         <is>
           <t>186910809.6</t>
         </is>
       </c>
-      <c r="AZ53" t="inlineStr">
-        <is>
-          <t>77335277.14</t>
-        </is>
+      <c r="AZ53" t="n">
+        <v>77335277.14</v>
       </c>
       <c r="BA53" t="inlineStr">
         <is>
@@ -23378,8 +23064,10 @@
           <t>23622172.09059471</t>
         </is>
       </c>
-      <c r="BD53" t="n">
-        <v>145797802</v>
+      <c r="BD53" t="inlineStr">
+        <is>
+          <t>145797802.0</t>
+        </is>
       </c>
       <c r="BE53" t="inlineStr">
         <is>
@@ -23545,7 +23233,7 @@
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
@@ -23729,15 +23417,11 @@
           <t>102.38</t>
         </is>
       </c>
-      <c r="AM54" t="inlineStr">
-        <is>
-          <t>94.8</t>
-        </is>
-      </c>
-      <c r="AN54" t="inlineStr">
-        <is>
-          <t>95.53</t>
-        </is>
+      <c r="AM54" t="n">
+        <v>94.8</v>
+      </c>
+      <c r="AN54" t="n">
+        <v>95.53</v>
       </c>
       <c r="AO54" t="inlineStr">
         <is>
@@ -23784,20 +23468,16 @@
           <t>156229829.0</t>
         </is>
       </c>
-      <c r="AX54" t="inlineStr">
-        <is>
-          <t>244853445.0</t>
-        </is>
+      <c r="AX54" t="n">
+        <v>244853445</v>
       </c>
       <c r="AY54" t="inlineStr">
         <is>
           <t>177136934.0</t>
         </is>
       </c>
-      <c r="AZ54" t="inlineStr">
-        <is>
-          <t>75407300.22</t>
-        </is>
+      <c r="AZ54" t="n">
+        <v>75407300.22</v>
       </c>
       <c r="BA54" t="inlineStr">
         <is>
@@ -23814,8 +23494,10 @@
           <t>30593803.45596609</t>
         </is>
       </c>
-      <c r="BD54" t="n">
-        <v>156229829</v>
+      <c r="BD54" t="inlineStr">
+        <is>
+          <t>156229829.0</t>
+        </is>
       </c>
       <c r="BE54" t="inlineStr">
         <is>
@@ -23981,7 +23663,7 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
@@ -24165,15 +23847,11 @@
           <t>100.68</t>
         </is>
       </c>
-      <c r="AM55" t="inlineStr">
-        <is>
-          <t>94.2</t>
-        </is>
-      </c>
-      <c r="AN55" t="inlineStr">
-        <is>
-          <t>95.39</t>
-        </is>
+      <c r="AM55" t="n">
+        <v>94.2</v>
+      </c>
+      <c r="AN55" t="n">
+        <v>95.39</v>
       </c>
       <c r="AO55" t="inlineStr">
         <is>
@@ -24220,20 +23898,16 @@
           <t>236763982.0</t>
         </is>
       </c>
-      <c r="AX55" t="inlineStr">
-        <is>
-          <t>260614613.2</t>
-        </is>
+      <c r="AX55" t="n">
+        <v>260614613.2</v>
       </c>
       <c r="AY55" t="inlineStr">
         <is>
           <t>164971086.0</t>
         </is>
       </c>
-      <c r="AZ55" t="inlineStr">
-        <is>
-          <t>73504886.64</t>
-        </is>
+      <c r="AZ55" t="n">
+        <v>73504886.64</v>
       </c>
       <c r="BA55" t="inlineStr">
         <is>
@@ -24250,8 +23924,10 @@
           <t>38342923.81878352</t>
         </is>
       </c>
-      <c r="BD55" t="n">
-        <v>236763982</v>
+      <c r="BD55" t="inlineStr">
+        <is>
+          <t>236763982.0</t>
+        </is>
       </c>
       <c r="BE55" t="inlineStr">
         <is>
@@ -24417,7 +24093,7 @@
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
@@ -24601,15 +24277,11 @@
           <t>98.6</t>
         </is>
       </c>
-      <c r="AM56" t="inlineStr">
-        <is>
-          <t>93.46</t>
-        </is>
-      </c>
-      <c r="AN56" t="inlineStr">
-        <is>
-          <t>95.28</t>
-        </is>
+      <c r="AM56" t="n">
+        <v>93.45999999999999</v>
+      </c>
+      <c r="AN56" t="n">
+        <v>95.28</v>
       </c>
       <c r="AO56" t="inlineStr">
         <is>
@@ -24656,20 +24328,16 @@
           <t>289128955.0</t>
         </is>
       </c>
-      <c r="AX56" t="inlineStr">
-        <is>
-          <t>240578101.6</t>
-        </is>
+      <c r="AX56" t="n">
+        <v>240578101.6</v>
       </c>
       <c r="AY56" t="inlineStr">
         <is>
           <t>146043684.0</t>
         </is>
       </c>
-      <c r="AZ56" t="inlineStr">
-        <is>
-          <t>69868524.62</t>
-        </is>
+      <c r="AZ56" t="n">
+        <v>69868524.62</v>
       </c>
       <c r="BA56" t="inlineStr">
         <is>
@@ -24686,8 +24354,10 @@
           <t>39415046.37928045</t>
         </is>
       </c>
-      <c r="BD56" t="n">
-        <v>289128955</v>
+      <c r="BD56" t="inlineStr">
+        <is>
+          <t>289128955.0</t>
+        </is>
       </c>
       <c r="BE56" t="inlineStr">
         <is>
@@ -24851,11 +24521,7 @@
       </c>
     </row>
     <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
+      <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
           <t>2476</t>
@@ -25037,41 +24703,37 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AM57" t="inlineStr">
+      <c r="AM57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AN57" t="n">
+        <v>0</v>
+      </c>
+      <c r="AO57" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AN57" t="inlineStr">
+      <c r="AP57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AQ57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AR57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="AS57" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AO57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AP57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR57" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
       <c r="AT57" t="inlineStr">
         <is>
           <t>0</t>
@@ -25092,20 +24754,16 @@
           <t>0</t>
         </is>
       </c>
-      <c r="AX57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AX57" t="n">
+        <v>0</v>
       </c>
       <c r="AY57" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="AZ57" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
+      <c r="AZ57" t="n">
+        <v>0</v>
       </c>
       <c r="BA57" t="inlineStr">
         <is>
@@ -25122,8 +24780,10 @@
           <t>0</t>
         </is>
       </c>
-      <c r="BD57" t="n">
-        <v>0</v>
+      <c r="BD57" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
       </c>
       <c r="BE57" t="inlineStr">
         <is>
